--- a/python-excel/uploads/plantilla_nueva.xlsx
+++ b/python-excel/uploads/plantilla_nueva.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECC2F2DB-BEE2-4447-AB64-121EF00E6591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A251EFAD-7F37-4282-8B92-0A2BB9F28BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2A7318D4-67A4-4F71-B788-9FB76C14E944}"/>
   </bookViews>
@@ -322,158 +322,161 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -881,687 +884,702 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="e" vm="1">
+      <c r="A1" s="44" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="4"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="49"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="4"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="49"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="4"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="49"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="7"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="50"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="8" t="s">
+      <c r="B5" s="43"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="11"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="20"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="36" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="37"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="11"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="20"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="36" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="37"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="11"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="20"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="12" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="11"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="20"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="38" t="s">
+      <c r="B9" s="36"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="H9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="39" t="s">
+      <c r="J9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="39" t="s">
+      <c r="K9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="L9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="39" t="s">
+      <c r="M9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="39" t="s">
+      <c r="N9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="40" t="s">
+      <c r="O9" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="43"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="12"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="24"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="24"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="24"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="24"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="24"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="24"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="3"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="24"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="24"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="24"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="3"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="24"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="3"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="24"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="3"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="24"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="3"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="24"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="3"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="24"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="3"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="35"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="52"/>
+      <c r="O25" s="53"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="35"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="15"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="14"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="24"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="3"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="24"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="3"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="24"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="3"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="14"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="24"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="3"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="14"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="24"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="3"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="14"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="24"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="3"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="24"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="3"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="28"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="32"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="5"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="44"/>
-      <c r="K35" s="44"/>
-      <c r="L35" s="44"/>
-      <c r="M35" s="44"/>
-      <c r="N35" s="44"/>
-      <c r="O35" s="45"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="46" t="s">
+      <c r="A36" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="47"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="49"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="50"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="59">
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="D25:O25"/>
-    <mergeCell ref="D26:O26"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
+  <mergeCells count="58">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D1:O4"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A35:C35"/>
@@ -1578,35 +1596,19 @@
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D1:O4"/>
+    <mergeCell ref="D26:O26"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="O9:O10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
